--- a/01_data/01_input_data/02_processed/01_paper_IAEE/01_data_sheets_input/paper_paris_2025_input_production_world.xlsx
+++ b/01_data/01_input_data/02_processed/01_paper_IAEE/01_data_sheets_input/paper_paris_2025_input_production_world.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\01_paper_IAEE\01_data_sheets_input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/mar_eco_cbs_dk/Documents/Desktop/hydrogen_grid/01_data/01_input_data/02_processed/01_paper_IAEE/01_data_sheets_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AD67FF-C58A-4F57-B988-1BB7F8458596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{61051CAB-F224-4792-AEE8-218AA7F2319D}"/>
+    <workbookView xWindow="14600" yWindow="-15930" windowWidth="18900" windowHeight="10720" xr2:uid="{61051CAB-F224-4792-AEE8-218AA7F2319D}"/>
   </bookViews>
   <sheets>
     <sheet name="gas_consumption_GWh-a" sheetId="1" r:id="rId1"/>
@@ -506,7 +506,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.81640625" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
